--- a/Uploads/1_new_1124.xlsx
+++ b/Uploads/1_new_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,22 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>عصير جهينة اورينتال خروب - 1 لتر</t>
+    <t>اد – مى كاتشب سكويز - 425 جم</t>
+  </si>
+  <si>
+    <t>أولويز ماكسى سميكة ناعمة بلمسة الألوڤيرا طويلة +4 مجانا- 26 فوطة</t>
+  </si>
+  <si>
+    <t>أولويز ماكسى سميكة ناعمة بلمسة الألوڤيرا طويلة جدا + 4 مجانا- 24 فوطة</t>
+  </si>
+  <si>
+    <t>أولويز ماكسى سميكة ناعمة للبشرة الحساسة طويلة جداً - 7 فوطة</t>
+  </si>
+  <si>
+    <t>أولويز ماكسى سميكة ناعمة حساس طويلة جدا + 6 مجانا- 26 فوطة</t>
+  </si>
+  <si>
+    <t>أولويز ماكسى سميكة ناعمة للبشرة الحساسة طويلة  + 6  فوط مجانا- 28 فوطة</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,19 +441,104 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>10605</v>
+        <v>25907</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>531</v>
+        <v>475</v>
       </c>
       <c r="E2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>26124</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>66</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>26125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>26126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>26127</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>26128</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/1_new_1124.xlsx
+++ b/Uploads/1_new_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="160">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,247 +37,343 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سمن كريستال ابيض - 1.5 كجم</t>
+    <t>ارز حبوبة رفيع - 1 كجم</t>
   </si>
   <si>
     <t>كوفى ميكس بونجورنو ظرف - 12 جم</t>
   </si>
   <si>
+    <t>كوفى ميكس بونجورنو فى الخمسينة - 6 جم</t>
+  </si>
+  <si>
+    <t>نسكافيه 3*1 - 18 جم</t>
+  </si>
+  <si>
+    <t>صلصة هارفست صفيح - 375 جم</t>
+  </si>
+  <si>
+    <t>عسل البوادى اسود - 355 جم</t>
+  </si>
+  <si>
+    <t>دقيق حبوبة - 1 كجم</t>
+  </si>
+  <si>
     <t>شاى ليبتون ناعم  - 250 جم</t>
   </si>
   <si>
-    <t>شاى ليبتون  ناعم  - 40 جم</t>
-  </si>
-  <si>
-    <t>تونة صن شاين مفتتة حار - 185 جم</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود محوج غامق - 100 جم</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود سادة فاتح - 100 جم</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود سادة فاتح - 200 جم</t>
+    <t>فجيتار كنور عادى - 35 جم</t>
+  </si>
+  <si>
+    <t>كنور مرقة دجاج 12 مكعب عبوة اقتصادية- 108 جم</t>
+  </si>
+  <si>
+    <t>كنور فيجيتار حار - 35 جم</t>
+  </si>
+  <si>
+    <t>عصير جهينة تفاح - 235 مل</t>
+  </si>
+  <si>
+    <t>عصير جهينة كوكتيل - 235 مل</t>
+  </si>
+  <si>
+    <t>عصير بيتى تفاح - 235 مل</t>
+  </si>
+  <si>
+    <t>عصير بيتى كوكتيل - 235 مل</t>
+  </si>
+  <si>
+    <t>عصير بيتى جوافة - 235 مل</t>
+  </si>
+  <si>
+    <t>عصير بيتى برتقال - 235 مل</t>
+  </si>
+  <si>
+    <t>عصير بيتى تفاح - 1 لتر</t>
+  </si>
+  <si>
+    <t>عصير بيتى كوكتيل - 1 لتر</t>
+  </si>
+  <si>
+    <t>عصير بيتى جوافة - 1 لتر</t>
+  </si>
+  <si>
+    <t>لبن بخيره - 1 لتر</t>
+  </si>
+  <si>
+    <t>مرقة دجاج كنور فاين فودز شريط - 8 جم</t>
+  </si>
+  <si>
+    <t>مرقة ماجى دجاج شريط - 8 جم</t>
+  </si>
+  <si>
+    <t>لبن جهينة مكس شوكولاتة - 200 مل</t>
+  </si>
+  <si>
+    <t>لبن جهينة مكس فراولة - 200 مل</t>
+  </si>
+  <si>
+    <t>البوادي حلاوة- 255 جم</t>
   </si>
   <si>
     <t>سائل اطباق وفير بلس ليمون اصفر - 4 كجم</t>
   </si>
   <si>
-    <t>حفاضات بامبرز عبوة التوفير مقاس 4 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>تايد مسحوق اوتوماتيك داوني - 2.5 كجم</t>
-  </si>
-  <si>
-    <t>لبن جهينة خالى الدسم - 1 لتر</t>
+    <t>عصير بيتى مانجو - 235 مل</t>
+  </si>
+  <si>
+    <t>عصير بيتى اناناس - 235 مل</t>
+  </si>
+  <si>
+    <t>فاين مناديل فلافي جيب- 10 باكت</t>
+  </si>
+  <si>
+    <t>البوادي حلاوة- 130 جم</t>
+  </si>
+  <si>
+    <t>طحينة البوادى - 125 جم</t>
+  </si>
+  <si>
+    <t>عصير تانج مانجو ظرف - 20 جم</t>
+  </si>
+  <si>
+    <t>صلصة هارفست ظرف - 30 جم</t>
+  </si>
+  <si>
+    <t>عصير جهينة جوافة - 235 مل</t>
+  </si>
+  <si>
+    <t>شويبس ليمون نعناع - 950 مل</t>
+  </si>
+  <si>
+    <t>لبن جهينة كامل الدسم - 200 مل</t>
   </si>
   <si>
     <t>لبن جهينة مكس موز - 200 مل</t>
   </si>
   <si>
+    <t>عصير جهينة مانجو - 1 لتر</t>
+  </si>
+  <si>
     <t>عصير جهينة تفاح - 1 لتر</t>
   </si>
   <si>
     <t>عصير جهينة برتقال - 1 لتر</t>
   </si>
   <si>
-    <t>زيت هدية خليط- 1 لتر</t>
-  </si>
-  <si>
-    <t>هدية زيت خليط- 0.7 لتر</t>
+    <t>عصير جهينة كوكتيل - 1 لتر</t>
+  </si>
+  <si>
+    <t>عصير جهينة جوافة - 1 لتر</t>
+  </si>
+  <si>
+    <t>عصير جهينة برتقال - 235 مل</t>
+  </si>
+  <si>
+    <t>عصير جهينة اناناس - 235 مل</t>
+  </si>
+  <si>
+    <t>مشروب كادبوري مشروب كاكاو - 30 جم</t>
+  </si>
+  <si>
+    <t>بيبسى كانز جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>سفن اب كانز جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>كنور خلطة بشاميل- 70 جم</t>
+  </si>
+  <si>
+    <t>عصير بيتى برتقال - 1 لتر</t>
+  </si>
+  <si>
+    <t>فاين فودز مرقة خضار 12 مكعب - 108 جم</t>
+  </si>
+  <si>
+    <t>بيبسى - 2.43 لتر</t>
+  </si>
+  <si>
+    <t>طحينة البوادى - 240 جم</t>
+  </si>
+  <si>
+    <t>بيبسى تربو - 390 مل</t>
   </si>
   <si>
     <t>تونة دولفين قطعة واحدة بارد - 200 جم</t>
   </si>
   <si>
+    <t>طحينة الرشيدى الميزان ظرف - 21 جم</t>
+  </si>
+  <si>
     <t>طحينة الرشيدى الميزان - 130 جم</t>
   </si>
   <si>
-    <t>%طحينة الرشيدى الميزان خصم 10 - 255 جم</t>
-  </si>
-  <si>
-    <t>فول تدميس الضحى - 500 جم</t>
-  </si>
-  <si>
-    <t>سلايت زيت عباد الشمس- 2.1 لتر</t>
-  </si>
-  <si>
-    <t>برسيل جل اوتوماتيك بلاك - 900 جم</t>
-  </si>
-  <si>
-    <t>اريال باور  جل نظافة و إنتعاش- 2.35 كجم</t>
+    <t>لبن المراعى كامل دسم بلاستيك - 1 لتر</t>
+  </si>
+  <si>
+    <t>بيبسى مينى تربو - 250 مل</t>
+  </si>
+  <si>
+    <t>طحينة الرشيدى الميزان - 500 جم</t>
+  </si>
+  <si>
+    <t>لبان كلورتس نعناع - 1.5 ج</t>
   </si>
   <si>
     <t>تونة دولفين مفتتة بارد - 140 جم</t>
   </si>
   <si>
-    <t>حفاضات مولفيكس جامبو مقاس 3 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>اوكسي سائل أطباق ليمون اصفر - 600 جم</t>
-  </si>
-  <si>
-    <t>شامبو كلير رجالى ازرق اخضر و اسود - 5 مل</t>
-  </si>
-  <si>
-    <t>اندومى فراخ كارى اكواب - 60 جم</t>
-  </si>
-  <si>
-    <t>اريال بور جل داوني- 2.35 كجم</t>
-  </si>
-  <si>
-    <t>طحينة البوادى - 480 جم</t>
-  </si>
-  <si>
-    <t>تودو براوني كيك شيكولاتة - 15 جنية</t>
-  </si>
-  <si>
-    <t>اولويز ماكسى سميكة فردى ملمس قطنى طويل - 8 فوطة</t>
-  </si>
-  <si>
-    <t>حفاضات بامبرز عبوة التوفير مقاس 1 - 60 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات بى بم مقاس 4 - 32 حفاضة</t>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>نسكافيه شوكولاتة 3*1 - 18 جم</t>
+  </si>
+  <si>
+    <t>كوفى بريك 2*1 - 11 جم</t>
+  </si>
+  <si>
+    <t>كابتشينو كوفى بريك فانيليا 8 ظرف - 18.5 جم</t>
+  </si>
+  <si>
+    <t>كابتشينو كوفى بريك موكا - 18.5 جم</t>
+  </si>
+  <si>
+    <t>كابتشينو كوفى بريك بندق 8 ظرف - 18.5 جم</t>
+  </si>
+  <si>
+    <t>كابتشينو كوفى بريك كلاسيك 8 ظرف - 18.5 جم</t>
+  </si>
+  <si>
+    <t>عسل البوادى اسود - 190 جم</t>
+  </si>
+  <si>
+    <t>البوادى حلاوة سادة- 550 جم</t>
+  </si>
+  <si>
+    <t>البوادى حلاوة سادة عائلى- 760 جم</t>
+  </si>
+  <si>
+    <t>شويبس جولد اناناس - 1.75 لتر</t>
+  </si>
+  <si>
+    <t>حفاضات جود كير مقاس 2 - 40 حفاضة</t>
   </si>
   <si>
     <t>حفاضات جود كير مقاس 3 - 40 حفاضة</t>
   </si>
   <si>
-    <t>مناديل زينة تواليت مضغوط - 2 رول</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>بسكويت جولى - 10 قطعه</t>
-  </si>
-  <si>
-    <t>مناديل زينة تواليت مضغوط 2 طبقة - 6 رول</t>
-  </si>
-  <si>
-    <t>فيبا سائل اطباق ليمون اصفر- 2 كجم</t>
-  </si>
-  <si>
-    <t>شوكولاتة جلاكسى سادة  - 30 جم</t>
-  </si>
-  <si>
-    <t>كلوركس كلور ابيض ليمون اصفر - 950 مل</t>
-  </si>
-  <si>
-    <t>مناديل فاميليا تواليت مضغوط 5 رول + 1 رول هدية - 6 رول</t>
-  </si>
-  <si>
-    <t>نسكافيه 2*1 بدون سكر 24 ظرف - 10 جم</t>
-  </si>
-  <si>
-    <t>جبنـة ابو الولد - 8 مثلث</t>
-  </si>
-  <si>
-    <t>حفاضات بى بم مقاس 3 - 32 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات بيبى جوى مضغوطة وسط مقاس 3 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات بيبى جوى مضغوطة جيب مانع للتسريب كبير مقاس 4 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود محوج وسط - 100 جم</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود سادة وسط - 200 جم</t>
+    <t>حفاضات جود كير مقاس 4 - 40 حفاضة</t>
+  </si>
+  <si>
+    <t>صابون جوى عرض خاص - 110 جم</t>
+  </si>
+  <si>
+    <t>نسكافيه 3*1 ريتش - 21 جم</t>
+  </si>
+  <si>
+    <t>حلاوة الرشيدى الميزان - 130 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة حار 170 جم + 30 جم - 200 جم</t>
+  </si>
+  <si>
+    <t>صلصة هاينز - 360 جم</t>
+  </si>
+  <si>
+    <t>فانتا تفاح احمر ستار - 320 مل</t>
   </si>
   <si>
     <t>حفاضات جود كير مقاس 6 - 40 حفاضة</t>
   </si>
   <si>
-    <t>شوكولاتة جلاكسى كرسبى - 30 جم</t>
-  </si>
-  <si>
-    <t>شوكولاتة جلاكسى كراميل - 34 جم</t>
-  </si>
-  <si>
     <t>لبان تشكلتس نعناع - 0.5 جنية</t>
   </si>
   <si>
     <t>لبان تشكلتس فراولة - 0.5 جنية</t>
   </si>
   <si>
-    <t>مولتو ماجنم شوكولاتة بالبندق - 15 جنية</t>
-  </si>
-  <si>
-    <t>كنور خلطه 11 بهار - 6 جم</t>
-  </si>
-  <si>
-    <t>جبنة عبور لاند رومى - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة عبور لاند شيدر - 500 جم</t>
+    <t>كنور خلطة بطاطس - 6 جم</t>
   </si>
   <si>
     <t>حفاضات جود كير مقاس 4 - 100 حفاضة</t>
   </si>
   <si>
+    <t>ستينج فراولة مينى تربو - 250 مل</t>
+  </si>
+  <si>
     <t>حفاضات مولفيكس حديث الولادة مقاس 1 - 60 حفاضة</t>
   </si>
   <si>
+    <t>سبرايت اكشن - 300 مل</t>
+  </si>
+  <si>
     <t>اندومى سوبر مى خضار جامبو عرض 44 كيس - 100 جم</t>
   </si>
   <si>
     <t>اندومى لحمة بيف جامبو عرض 44 كيس - 100 جم</t>
   </si>
   <si>
-    <t>كابتشينو بونجورنو فانيليا - 14 جم</t>
-  </si>
-  <si>
-    <t>كابتشينو بونجورنو موكا 12 ظرف - 14 جم</t>
-  </si>
-  <si>
-    <t>_اريال اوتوماتيك داوني - 2.5 كجم</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
+    <t>اندومى فراخ جامبو عرض 44 كيس - 100 جم</t>
+  </si>
+  <si>
+    <t>كلوركس الوان ظرف - 210 جم</t>
+  </si>
+  <si>
+    <t>مايونيز هاينز الكبير - 14 جم</t>
+  </si>
+  <si>
+    <t>حلاوة بار الرشيدى الميزان - 21 جم</t>
+  </si>
+  <si>
+    <t>كاتشب هاينز اسكويزى دوى باك - 285 جم</t>
+  </si>
+  <si>
+    <t>مكرونة بساطة خواتم - 350 جم</t>
   </si>
   <si>
     <t>مكرونة بساطة فرن - 350 جم</t>
   </si>
   <si>
-    <t>شاى العروسة -..0 100 جم</t>
-  </si>
-  <si>
-    <t>حفاضات بامبرز بانتس مقاس 5 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فيبا سائل أطباق تفاح- 2 كجم</t>
-  </si>
-  <si>
-    <t>مسحوق باهى يدوى لافندر - 1.5 كجم</t>
-  </si>
-  <si>
-    <t>حفاضات بامبرز بيبى دراى عبوة التوفير مقاس 6 - 48 حفاضة</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس - 5 لتر</t>
-  </si>
-  <si>
-    <t>بريكس كلور ابيض - 950 مل</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل فل اوتوماتيك - 12 كجم</t>
-  </si>
-  <si>
-    <t>سمن كريستال اصفر 6 عبوة - 700 جم</t>
-  </si>
-  <si>
-    <t>ريف ويفر بحشو كريمة الشيكولاتة - 10 جنية</t>
-  </si>
-  <si>
-    <t>عصير جهينة بيور اناناس - 235 مل</t>
+    <t>مكرونة بساطة مرمرية - 350 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى كلاسيك -- 110 جم</t>
+  </si>
+  <si>
+    <t>شويبس جولد اناناس - 950 مل</t>
+  </si>
+  <si>
+    <t>شويبس رمان - 950 مل</t>
+  </si>
+  <si>
+    <t>ماكسى ليمون - 400 مل</t>
+  </si>
+  <si>
+    <t>ماكسى شعير اناناس - 400 مل</t>
+  </si>
+  <si>
+    <t>ماكسى برتقال - 400 مل</t>
+  </si>
+  <si>
+    <t>فانتا برتقال اكشن - 300 مل</t>
+  </si>
+  <si>
+    <t>بيبسى - 1.47 لتر</t>
+  </si>
+  <si>
+    <t>طحينة البوادى ظرف - 22 جرام</t>
+  </si>
+  <si>
+    <t>البوادي حلاوة بار  - 18 جم</t>
+  </si>
+  <si>
+    <t>كاتشب هاينز الكبير - 14 جم</t>
+  </si>
+  <si>
+    <t>كاتشب هاينز اسكويزى دوى باك - 125 جم</t>
   </si>
   <si>
     <t>عصير جهينة بيور تفاح - 235 مل</t>
@@ -289,160 +385,112 @@
     <t>عصير جهينة بيور جوافة كوكتيل - 235 مل</t>
   </si>
   <si>
-    <t>شاى ليبتون اخضر - 25 فتلة</t>
-  </si>
-  <si>
-    <t>شاى ليبتون اخضر بالنعناع - 25 فتلة</t>
-  </si>
-  <si>
-    <t>مسحوق باهى لافندر اوتوماتيك 8 ك + 1 ك - 9 كجم</t>
-  </si>
-  <si>
-    <t>مناديل زينة فاليو مطبخ 5 + 1 رول هدية - 6 رول</t>
-  </si>
-  <si>
-    <t>شوكولاتة جلاكسى دارك كريم - 33 جم</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فلمنك - 125 جم</t>
+    <t>مربى البوادى فراولة - 680 جم</t>
   </si>
   <si>
     <t>مربى البوادى تين - 365 جم</t>
   </si>
   <si>
-    <t>العبد كوكيز فانيليا بقطع الشكولاتة - 29 جنية</t>
-  </si>
-  <si>
-    <t>مسحوق ليدر عادى ياسمين - 65 جم</t>
-  </si>
-  <si>
-    <t>حفاضات بيبى جوى مضغوطة مقاس 1 - 60 حفاضة</t>
-  </si>
-  <si>
-    <t>شامبو كلير حريمى بامبى - 5 مل</t>
+    <t>كوفى بريك 3*1 - 18 جم</t>
+  </si>
+  <si>
+    <t>لبن المراعى كامل الدسم - 1.5 لتر</t>
+  </si>
+  <si>
+    <t>اوكسى جل بلاك - 90 جم</t>
+  </si>
+  <si>
+    <t>اوكسى يدوى - 1 كجم</t>
+  </si>
+  <si>
+    <t>ستينج فراولة تربو بلاستيك - 400 مل</t>
   </si>
   <si>
     <t>لبن جهينة مكس كراميل - 200 مل</t>
   </si>
   <si>
-    <t>عصير جهينة تفاح كمثرى - 235 مل</t>
-  </si>
-  <si>
-    <t>اوكسى سائل اطباق ليمون أخضر ظرف 35 جرام</t>
-  </si>
-  <si>
-    <t>اوكسي سائل أطباق ليمون اصفر - 350 جم</t>
-  </si>
-  <si>
-    <t>سائل اطباق وفير بلس ليمون اصفر - 40 جم</t>
-  </si>
-  <si>
-    <t>سائل اطباق وفير بلس ليمون اخضر - 40 جم</t>
+    <t>عصير جهينة مكس بيرى - 235 مل</t>
   </si>
   <si>
     <t>المراعي جبنة فيتا - 250 جم</t>
   </si>
   <si>
-    <t>اوكسى يدوى - 330 جم</t>
-  </si>
-  <si>
-    <t>اوكسى يدوى - 250 جم</t>
-  </si>
-  <si>
-    <t>باهي مسحوق يدوي بالافندر - 410 جم</t>
-  </si>
-  <si>
-    <t>مسحوق باهى يدوى لافندر - 215 جم</t>
-  </si>
-  <si>
-    <t>كل يوم عصير جوافة  - 200 مل</t>
-  </si>
-  <si>
-    <t>مولتو ميني ماجنم ميكس تشيز كيك فراولة و كريمة - 15 جنية</t>
-  </si>
-  <si>
-    <t>بسكويت اولكر بالتمر 6 قطع - 7 جنية</t>
+    <t>المراعي جبنة فيتا بالرومي - 250 جم</t>
+  </si>
+  <si>
+    <t>زيووو إكسترا كرانشى طماطم - 5 جنية</t>
+  </si>
+  <si>
+    <t>زيووو كرانشى الشطة الحار - 5 جنية</t>
+  </si>
+  <si>
+    <t>زيووو كرانشى الجبنة - 5 جنية</t>
   </si>
   <si>
     <t>زيووو شرائح كيرلي خضروات - 5 جنية</t>
   </si>
   <si>
+    <t>زيووو شرائح كيرليى بيتزا - 5 جنية</t>
+  </si>
+  <si>
     <t>زيووو اراميش بافس جبنة - 5 جنية</t>
   </si>
   <si>
+    <t>زيووو اراميش بافس فلفل حلو - 5 جنية</t>
+  </si>
+  <si>
+    <t>زيووو اراميش بافس سجق - 5 جنية</t>
+  </si>
+  <si>
     <t>جل باهى لافندر - 40 جم</t>
   </si>
   <si>
-    <t>برسيل يدوى لافندر - 200 جم</t>
-  </si>
-  <si>
-    <t>فرسكا شوكوبار مغطى بالشوكولاتة -حجم اكبر 5 جنية</t>
-  </si>
-  <si>
-    <t>فرسكا شوكو بار حلاوة12 قطعه حجم اكبر 5 جنية</t>
-  </si>
-  <si>
-    <t>اريال يدوى لافندر جل- 730 جم</t>
-  </si>
-  <si>
-    <t>-أريال يدوى لافندر 1 كجم</t>
-  </si>
-  <si>
     <t>ماكسى برتقال - 1 لتر</t>
   </si>
   <si>
-    <t>لارش ميلت كيك بصوص الكاكاو ومغطي بالكاكاو - 10 جنية</t>
-  </si>
-  <si>
-    <t>شوكولاتة كادبورى بندق 15 جنيه - 18.5 جم</t>
-  </si>
-  <si>
-    <t>بسكويت اوريو اوريجنال - 720 جرام</t>
-  </si>
-  <si>
-    <t>فاتيكا زيت شعر  الالوفيرا خصم %10- 180 مل</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة اسطنبولي بلس - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس لايت - 500 جم</t>
-  </si>
-  <si>
-    <t>شورتى بسكويت - 10 جنية</t>
-  </si>
-  <si>
-    <t>فيانسيه شامبو 7فى1 اكياس بالأفوكادووالزيتون 5 مل</t>
-  </si>
-  <si>
-    <t>بقسماط ناعم ريتش بيك - 400 جرام</t>
-  </si>
-  <si>
-    <t>ماندولين ويفر جديد 10 جنيه  - 33 جم</t>
-  </si>
-  <si>
-    <t>كوكيز العبد فانيليا - 18 قطعه</t>
-  </si>
-  <si>
-    <t>علبة كوكيز ميكس - 18 قطعه</t>
-  </si>
-  <si>
-    <t>ماكينة حلاقة جيليت فينوس ديسي 2 حريمى حصيرة - 48 ماكينة</t>
+    <t>ماكسى كولا - 1 لتر</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
+  </si>
+  <si>
+    <t>مكرونة بساطة اسباجيتى - 1 كجم</t>
+  </si>
+  <si>
+    <t>كوكا كولا زيرو 10% زياده - 355 مل</t>
+  </si>
+  <si>
+    <t>اندومي سوبر مى خضار حارجامبو عرض 44 كيس - 100 جم</t>
+  </si>
+  <si>
+    <t>اوكسي يدوي 32 كيس - 50 جم</t>
+  </si>
+  <si>
+    <t>اوكسي يدوي مسحوق 24 كيس - 110 جم</t>
+  </si>
+  <si>
+    <t>ماندولين ويفر كريمة الكاكاو ب 5ج - 16 جم</t>
+  </si>
+  <si>
+    <t>بونجورنو  كوفي مزاجو ميكس 4*1 - 15 جرام</t>
+  </si>
+  <si>
+    <t>مولفيكس بانتس مقاس 4 - 56 حفاضة</t>
+  </si>
+  <si>
+    <t>مولفيكس بانتس  مقاس 6 كبير جدا 46 حفاضة</t>
+  </si>
+  <si>
+    <t>مشروب بودرة تانج مانجو جديد 2 لتر - 40 جرام</t>
   </si>
   <si>
     <t>اندومى فراخ - 5 جنية 56 جم</t>
   </si>
   <si>
-    <t>اندومى سوبر مى خضار - 5 جنيه - 56 جم</t>
-  </si>
-  <si>
-    <t>مسحوق باهى يدوى لافندر 12 كيس- 135 جم</t>
+    <t>اندومى لحمة بيف  -5جنيه - 56 جم</t>
+  </si>
+  <si>
+    <t>ماكسى ليمون نعناع - 1 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -803,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -831,19 +879,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>600</v>
+        <v>254.5</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -860,7 +908,7 @@
         <v>1675</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -877,12 +925,12 @@
         <v>69.75</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -891,32 +939,32 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2499.75</v>
+        <v>873.5</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>52</v>
+        <v>36.5</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -925,32 +973,32 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>2880</v>
+        <v>1680</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -959,15 +1007,15 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1704</v>
+        <v>767.5</v>
       </c>
       <c r="E9" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -976,1851 +1024,1851 @@
         <v>11</v>
       </c>
       <c r="D10">
-        <v>35.5</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>216</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <v>8652</v>
+        <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>216</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D12">
-        <v>721</v>
+        <v>383.75</v>
       </c>
       <c r="E12" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>7587</v>
+        <v>540</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>632.25</v>
+        <v>22.5</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>221</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D15">
-        <v>6798</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>221</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D16">
-        <v>566.5</v>
+        <v>270</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>322</v>
+        <v>202.25</v>
       </c>
       <c r="E17" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>334</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>1020</v>
+        <v>2512.75</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>334</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>340</v>
+        <v>52.25</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>409</v>
+        <v>105</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>540</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>411</v>
+        <v>110</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>284.75</v>
+        <v>1152</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>413</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>349</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>414</v>
+        <v>114</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>340</v>
+        <v>720</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>479</v>
+        <v>114</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>884.25</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>924</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>614</v>
+        <v>189</v>
       </c>
       <c r="E26" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>947</v>
+        <v>142</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>2880</v>
+        <v>191.25</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>947</v>
+        <v>143</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C28">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>60</v>
+        <v>189.25</v>
       </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>947</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>720</v>
+        <v>189.25</v>
       </c>
       <c r="E29" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>947</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C30">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>1440</v>
+        <v>189.25</v>
       </c>
       <c r="E30" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>964</v>
+        <v>146</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>1090</v>
+        <v>189.25</v>
       </c>
       <c r="E31" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>964</v>
+        <v>147</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>27.25</v>
+        <v>336</v>
       </c>
       <c r="E32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>964</v>
+        <v>148</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
       <c r="C33">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>272.5</v>
+        <v>336</v>
       </c>
       <c r="E33" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>964</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C34">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>545</v>
+        <v>336</v>
       </c>
       <c r="E34" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>965</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35">
-        <v>1238.5</v>
+        <v>441</v>
       </c>
       <c r="E35" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>965</v>
+        <v>159</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>51.5</v>
+        <v>735</v>
       </c>
       <c r="E36" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>1069</v>
+        <v>159</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>1070</v>
+        <v>40.75</v>
       </c>
       <c r="E37" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>1069</v>
+        <v>159</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D38">
-        <v>53.5</v>
+        <v>367.5</v>
       </c>
       <c r="E38" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>1084</v>
+        <v>161</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39">
-        <v>738.25</v>
+        <v>747</v>
       </c>
       <c r="E39" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>1116</v>
+        <v>161</v>
       </c>
       <c r="B40" t="s">
         <v>29</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>415</v>
+        <v>41.5</v>
       </c>
       <c r="E40" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>1134</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s">
         <v>30</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>680</v>
+        <v>273.75</v>
       </c>
       <c r="E41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>1413</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
         <v>31</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>1177.5</v>
+        <v>274.75</v>
       </c>
       <c r="E42" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>1413</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>24.5</v>
+        <v>1064.5</v>
       </c>
       <c r="E43" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>1413</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>294.5</v>
+        <v>44.25</v>
       </c>
       <c r="E44" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>1413</v>
+        <v>247</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C45">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>588.75</v>
+        <v>318</v>
       </c>
       <c r="E45" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>1432</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46">
-        <v>945</v>
+        <v>197.25</v>
       </c>
       <c r="E46" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>1432</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C47">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>315</v>
+        <v>196.5</v>
       </c>
       <c r="E47" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>1668</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48">
-        <v>303.75</v>
+        <v>179.25</v>
       </c>
       <c r="E48" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>1801</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49">
-        <v>308</v>
+        <v>1106.25</v>
       </c>
       <c r="E49" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>1851</v>
+        <v>335</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>344</v>
+        <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>1988</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51">
-        <v>680</v>
+        <v>1050</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>2105</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D52">
-        <v>1188</v>
+        <v>26.25</v>
       </c>
       <c r="E52" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>2105</v>
+        <v>336</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D53">
-        <v>99</v>
+        <v>262.5</v>
       </c>
       <c r="E53" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>2169</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s">
         <v>38</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D54">
-        <v>609</v>
+        <v>525</v>
       </c>
       <c r="E54" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>2169</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>101.5</v>
+        <v>960</v>
       </c>
       <c r="E55" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>2216</v>
+        <v>345</v>
       </c>
       <c r="B56" t="s">
         <v>39</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>376</v>
+        <v>96</v>
       </c>
       <c r="E56" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>2216</v>
+        <v>346</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>23.5</v>
+        <v>203</v>
       </c>
       <c r="E57" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>2216</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C58">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D58">
-        <v>94</v>
+        <v>50.75</v>
       </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>2216</v>
+        <v>361</v>
       </c>
       <c r="B59" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C59">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E59" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>2308</v>
+        <v>378</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C60">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="E60" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>2308</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C61">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>885</v>
+        <v>280</v>
       </c>
       <c r="E61" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>2406</v>
+        <v>411</v>
       </c>
       <c r="B62" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C62">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>583</v>
+        <v>278.75</v>
       </c>
       <c r="E62" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>2406</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C63">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>145.75</v>
+        <v>361</v>
       </c>
       <c r="E63" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>2422</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C64">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>788.75</v>
+        <v>348</v>
       </c>
       <c r="E64" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>2422</v>
+        <v>414</v>
       </c>
       <c r="B65" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C65">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>157.75</v>
+        <v>345</v>
       </c>
       <c r="E65" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>2528</v>
+        <v>415</v>
       </c>
       <c r="B66" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C66">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>305</v>
+        <v>348</v>
       </c>
       <c r="E66" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>2879</v>
+        <v>416</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C67">
         <v>1</v>
       </c>
       <c r="D67">
-        <v>797.25</v>
+        <v>349.5</v>
       </c>
       <c r="E67" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>2934</v>
+        <v>417</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>1056</v>
+        <v>189</v>
       </c>
       <c r="E68" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>2992</v>
+        <v>418</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>862.75</v>
+        <v>214</v>
       </c>
       <c r="E69" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>2992</v>
+        <v>432</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>215.75</v>
+        <v>825</v>
       </c>
       <c r="E70" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>3278</v>
+        <v>432</v>
       </c>
       <c r="B71" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C71">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D71">
-        <v>290</v>
+        <v>103.25</v>
       </c>
       <c r="E71" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>3338</v>
+        <v>434</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>276</v>
+        <v>298.5</v>
       </c>
       <c r="E72" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>3379</v>
+        <v>435</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73">
-        <v>4560</v>
+        <v>294.25</v>
       </c>
       <c r="E73" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>3379</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>380</v>
+        <v>893.25</v>
       </c>
       <c r="E74" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>3386</v>
+        <v>440</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75">
-        <v>330</v>
+        <v>149</v>
       </c>
       <c r="E75" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>3442</v>
+        <v>506</v>
       </c>
       <c r="B76" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C76">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="E76" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>3456</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77">
-        <v>1647.5</v>
+        <v>1152</v>
       </c>
       <c r="E77" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>3456</v>
+        <v>515</v>
       </c>
       <c r="B78" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D78">
-        <v>137.25</v>
+        <v>144</v>
       </c>
       <c r="E78" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>3495</v>
+        <v>589</v>
       </c>
       <c r="B79" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79">
-        <v>1191.75</v>
+        <v>219.5</v>
       </c>
       <c r="E79" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>3495</v>
+        <v>590</v>
       </c>
       <c r="B80" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>29.75</v>
+        <v>1207.5</v>
       </c>
       <c r="E80" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>3549</v>
+        <v>590</v>
       </c>
       <c r="B81" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C81">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D81">
-        <v>150</v>
+        <v>50.25</v>
       </c>
       <c r="E81" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>3549</v>
+        <v>590</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C82">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D82">
-        <v>600</v>
+        <v>301.75</v>
       </c>
       <c r="E82" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>3575</v>
+        <v>590</v>
       </c>
       <c r="B83" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C83">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D83">
-        <v>290</v>
+        <v>603.75</v>
       </c>
       <c r="E83" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>3575</v>
+        <v>593</v>
       </c>
       <c r="B84" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C84">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>870</v>
+        <v>130</v>
       </c>
       <c r="E84" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>3576</v>
+        <v>947</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C85">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>290</v>
+        <v>2844</v>
       </c>
       <c r="E85" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>3576</v>
+        <v>947</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C86">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D86">
-        <v>870</v>
+        <v>59.25</v>
       </c>
       <c r="E86" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>4223</v>
+        <v>947</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D87">
-        <v>8400</v>
+        <v>711</v>
       </c>
       <c r="E87" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>4223</v>
+        <v>947</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C88">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D88">
-        <v>700</v>
+        <v>1422</v>
       </c>
       <c r="E88" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>4224</v>
+        <v>963</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89">
-        <v>6798</v>
+        <v>451.25</v>
       </c>
       <c r="E89" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>4224</v>
+        <v>963</v>
       </c>
       <c r="B90" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90">
-        <v>566.5</v>
+        <v>75.25</v>
       </c>
       <c r="E90" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>4232</v>
+        <v>964</v>
       </c>
       <c r="B91" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C91">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>990.75</v>
+        <v>1090</v>
       </c>
       <c r="E91" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>4232</v>
+        <v>964</v>
       </c>
       <c r="B92" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C92">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="D92">
-        <v>198.25</v>
+        <v>27.25</v>
       </c>
       <c r="E92" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>4719</v>
+        <v>964</v>
       </c>
       <c r="B93" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D93">
-        <v>4758</v>
+        <v>272.5</v>
       </c>
       <c r="E93" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>4719</v>
+        <v>964</v>
       </c>
       <c r="B94" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D94">
-        <v>396.5</v>
+        <v>545</v>
       </c>
       <c r="E94" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>4720</v>
+        <v>990</v>
       </c>
       <c r="B95" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95">
-        <v>4758</v>
+        <v>561.25</v>
       </c>
       <c r="E95" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>4720</v>
+        <v>1007</v>
       </c>
       <c r="B96" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D96">
-        <v>396.5</v>
+        <v>109.75</v>
       </c>
       <c r="E96" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>5208</v>
+        <v>1054</v>
       </c>
       <c r="B97" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>1650</v>
+        <v>1236</v>
       </c>
       <c r="E97" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>5208</v>
+        <v>1054</v>
       </c>
       <c r="B98" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D98">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="E98" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>5209</v>
+        <v>1163</v>
       </c>
       <c r="B99" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99">
-        <v>1650</v>
+        <v>1688</v>
       </c>
       <c r="E99" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>5209</v>
+        <v>1163</v>
       </c>
       <c r="B100" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C100">
         <v>3</v>
       </c>
       <c r="D100">
-        <v>55</v>
+        <v>84.5</v>
       </c>
       <c r="E100" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>5453</v>
+        <v>1413</v>
       </c>
       <c r="B101" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
       <c r="D101">
-        <v>291</v>
+        <v>1177.5</v>
       </c>
       <c r="E101" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>5585</v>
+        <v>1413</v>
       </c>
       <c r="B102" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D102">
-        <v>1228.5</v>
+        <v>24.5</v>
       </c>
       <c r="E102" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>5585</v>
+        <v>1413</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D103">
-        <v>122.75</v>
+        <v>294.5</v>
       </c>
       <c r="E103" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>5647</v>
+        <v>1413</v>
       </c>
       <c r="B104" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D104">
-        <v>475</v>
+        <v>588.75</v>
       </c>
       <c r="E104" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>5649</v>
+        <v>1490</v>
       </c>
       <c r="B105" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>462</v>
+        <v>588</v>
       </c>
       <c r="E105" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>6098</v>
+        <v>1492</v>
       </c>
       <c r="B106" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C106">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>773</v>
+        <v>803</v>
       </c>
       <c r="E106" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>6098</v>
+        <v>1699</v>
       </c>
       <c r="B107" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C107">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>386.5</v>
+        <v>1650</v>
       </c>
       <c r="E107" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>6872</v>
+        <v>1699</v>
       </c>
       <c r="B108" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C108">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D108">
-        <v>261</v>
+        <v>137.5</v>
       </c>
       <c r="E108" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>6872</v>
+        <v>2049</v>
       </c>
       <c r="B109" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C109">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>783</v>
+        <v>1285</v>
       </c>
       <c r="E109" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>7004</v>
+        <v>2049</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D110">
-        <v>369.5</v>
+        <v>53.5</v>
       </c>
       <c r="E110" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>7005</v>
+        <v>2050</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C111">
         <v>1</v>
       </c>
       <c r="D111">
-        <v>375</v>
+        <v>1588.75</v>
       </c>
       <c r="E111" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>7119</v>
+        <v>2050</v>
       </c>
       <c r="B112" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D112">
-        <v>1668</v>
+        <v>66.25</v>
       </c>
       <c r="E112" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>7119</v>
+        <v>2054</v>
       </c>
       <c r="B113" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>104.25</v>
+        <v>1514.5</v>
       </c>
       <c r="E113" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>7122</v>
+        <v>2054</v>
       </c>
       <c r="B114" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D114">
-        <v>1667.5</v>
+        <v>63</v>
       </c>
       <c r="E114" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>7122</v>
+        <v>2055</v>
       </c>
       <c r="B115" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115">
-        <v>104.25</v>
+        <v>1536</v>
       </c>
       <c r="E115" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>7204</v>
+        <v>2055</v>
       </c>
       <c r="B116" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D116">
-        <v>775</v>
+        <v>64</v>
       </c>
       <c r="E116" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>7324</v>
+        <v>2057</v>
       </c>
       <c r="B117" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117">
-        <v>482.5</v>
+        <v>1540.5</v>
       </c>
       <c r="E117" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>7705</v>
+        <v>2057</v>
       </c>
       <c r="B118" t="s">
         <v>76</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D118">
-        <v>168.5</v>
+        <v>64.25</v>
       </c>
       <c r="E118" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>7887</v>
+        <v>2103</v>
       </c>
       <c r="B119" t="s">
         <v>77</v>
@@ -2829,1472 +2877,1982 @@
         <v>1</v>
       </c>
       <c r="D119">
-        <v>2511.5</v>
+        <v>351.25</v>
       </c>
       <c r="E119" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>7887</v>
+        <v>2103</v>
       </c>
       <c r="B120" t="s">
         <v>77</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D120">
-        <v>209.25</v>
+        <v>14.75</v>
       </c>
       <c r="E120" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>8155</v>
+        <v>2103</v>
       </c>
       <c r="B121" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D121">
-        <v>1099.75</v>
+        <v>87.75</v>
       </c>
       <c r="E121" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122">
-        <v>8155</v>
+        <v>2103</v>
       </c>
       <c r="B122" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C122">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D122">
-        <v>366.5</v>
+        <v>175.5</v>
       </c>
       <c r="E122" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>8360</v>
+        <v>2104</v>
       </c>
       <c r="B123" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C123">
         <v>1</v>
       </c>
       <c r="D123">
-        <v>287.5</v>
+        <v>1077.5</v>
       </c>
       <c r="E123" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>8659</v>
+        <v>2104</v>
       </c>
       <c r="B124" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D124">
-        <v>241.25</v>
+        <v>89.75</v>
       </c>
       <c r="E124" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125">
-        <v>8907</v>
+        <v>2108</v>
       </c>
       <c r="B125" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C125">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D125">
-        <v>430.5</v>
+        <v>691.25</v>
       </c>
       <c r="E125" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126">
-        <v>8907</v>
+        <v>2108</v>
       </c>
       <c r="B126" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C126">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D126">
-        <v>1291.75</v>
+        <v>115.25</v>
       </c>
       <c r="E126" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127">
-        <v>9070</v>
+        <v>2327</v>
       </c>
       <c r="B127" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127">
-        <v>890</v>
+        <v>223.75</v>
       </c>
       <c r="E127" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128">
-        <v>9182</v>
+        <v>2421</v>
       </c>
       <c r="B128" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D128">
-        <v>189</v>
+        <v>692.5</v>
       </c>
       <c r="E128" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129">
-        <v>9373</v>
+        <v>2421</v>
       </c>
       <c r="B129" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C129">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="D129">
-        <v>327</v>
+        <v>138.5</v>
       </c>
       <c r="E129" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130">
-        <v>9613</v>
+        <v>2422</v>
       </c>
       <c r="B130" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D130">
-        <v>465</v>
+        <v>801</v>
       </c>
       <c r="E130" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131">
-        <v>9623</v>
+        <v>2422</v>
       </c>
       <c r="B131" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D131">
-        <v>847.25</v>
+        <v>160.25</v>
       </c>
       <c r="E131" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132">
-        <v>9623</v>
+        <v>2423</v>
       </c>
       <c r="B132" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D132">
-        <v>141.25</v>
+        <v>796.5</v>
       </c>
       <c r="E132" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133">
-        <v>9783</v>
+        <v>2423</v>
       </c>
       <c r="B133" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D133">
-        <v>448</v>
+        <v>159.25</v>
       </c>
       <c r="E133" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134">
-        <v>9784</v>
+        <v>2438</v>
       </c>
       <c r="B134" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="D134">
-        <v>403.5</v>
+        <v>555</v>
       </c>
       <c r="E134" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135">
-        <v>9785</v>
+        <v>2438</v>
       </c>
       <c r="B135" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D135">
-        <v>405</v>
+        <v>46.25</v>
       </c>
       <c r="E135" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136">
-        <v>9786</v>
+        <v>2703</v>
       </c>
       <c r="B136" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C136">
         <v>1</v>
       </c>
       <c r="D136">
-        <v>406</v>
+        <v>2508</v>
       </c>
       <c r="E136" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137">
-        <v>9796</v>
+        <v>2703</v>
       </c>
       <c r="B137" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D137">
-        <v>1418.5</v>
+        <v>104.5</v>
       </c>
       <c r="E137" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138">
-        <v>9796</v>
+        <v>2821</v>
       </c>
       <c r="B138" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C138">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D138">
-        <v>29.5</v>
+        <v>565.25</v>
       </c>
       <c r="E138" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139">
-        <v>9797</v>
+        <v>2821</v>
       </c>
       <c r="B139" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139">
-        <v>1441.25</v>
+        <v>23.5</v>
       </c>
       <c r="E139" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140">
-        <v>9797</v>
+        <v>2859</v>
       </c>
       <c r="B140" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C140">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140">
-        <v>30</v>
+        <v>1680</v>
       </c>
       <c r="E140" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141">
-        <v>10174</v>
+        <v>2859</v>
       </c>
       <c r="B141" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D141">
-        <v>741</v>
+        <v>35</v>
       </c>
       <c r="E141" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142">
-        <v>10176</v>
+        <v>2859</v>
       </c>
       <c r="B142" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C142">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D142">
-        <v>221</v>
+        <v>420</v>
       </c>
       <c r="E142" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143">
-        <v>10382</v>
+        <v>2859</v>
       </c>
       <c r="B143" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D143">
-        <v>4800</v>
+        <v>840</v>
       </c>
       <c r="E143" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144">
-        <v>10382</v>
+        <v>3478</v>
       </c>
       <c r="B144" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D144">
-        <v>400</v>
+        <v>386.75</v>
       </c>
       <c r="E144" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145">
-        <v>10391</v>
+        <v>3671</v>
       </c>
       <c r="B145" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145">
-        <v>402</v>
+        <v>329.75</v>
       </c>
       <c r="E145" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146">
-        <v>10410</v>
+        <v>4232</v>
       </c>
       <c r="B146" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D146">
-        <v>321</v>
+        <v>990.75</v>
       </c>
       <c r="E146" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147">
-        <v>10410</v>
+        <v>4232</v>
       </c>
       <c r="B147" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C147">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D147">
-        <v>26.75</v>
+        <v>198.25</v>
       </c>
       <c r="E147" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148">
-        <v>10580</v>
+        <v>5208</v>
       </c>
       <c r="B148" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148">
-        <v>1836</v>
+        <v>1603.5</v>
       </c>
       <c r="E148" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149">
-        <v>10580</v>
+        <v>5208</v>
       </c>
       <c r="B149" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C149">
         <v>3</v>
       </c>
       <c r="D149">
-        <v>153</v>
+        <v>53.5</v>
       </c>
       <c r="E149" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150">
-        <v>10898</v>
+        <v>5209</v>
       </c>
       <c r="B150" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150">
-        <v>133</v>
+        <v>1618.5</v>
       </c>
       <c r="E150" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151">
-        <v>11425</v>
+        <v>5209</v>
       </c>
       <c r="B151" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C151">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D151">
-        <v>256.25</v>
+        <v>54</v>
       </c>
       <c r="E151" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152">
-        <v>11425</v>
+        <v>5584</v>
       </c>
       <c r="B152" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C152">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D152">
-        <v>769</v>
+        <v>1225</v>
       </c>
       <c r="E152" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153">
-        <v>11467</v>
+        <v>5584</v>
       </c>
       <c r="B153" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153">
-        <v>320</v>
+        <v>122.5</v>
       </c>
       <c r="E153" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154">
-        <v>11490</v>
+        <v>6098</v>
       </c>
       <c r="B154" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D154">
-        <v>275</v>
+        <v>774.5</v>
       </c>
       <c r="E154" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155">
-        <v>11491</v>
+        <v>6098</v>
       </c>
       <c r="B155" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D155">
-        <v>214</v>
+        <v>387.25</v>
       </c>
       <c r="E155" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156">
-        <v>11586</v>
+        <v>6158</v>
       </c>
       <c r="B156" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156">
-        <v>87.25</v>
+        <v>113</v>
       </c>
       <c r="E156" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157">
-        <v>11618</v>
+        <v>6872</v>
       </c>
       <c r="B157" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D157">
-        <v>180</v>
+        <v>270.5</v>
       </c>
       <c r="E157" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158">
-        <v>11677</v>
+        <v>6872</v>
       </c>
       <c r="B158" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C158">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D158">
-        <v>65</v>
+        <v>811.5</v>
       </c>
       <c r="E158" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159">
-        <v>11678</v>
+        <v>6936</v>
       </c>
       <c r="B159" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="E159" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160">
-        <v>11737</v>
+        <v>7004</v>
       </c>
       <c r="B160" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160">
-        <v>497</v>
+        <v>369</v>
       </c>
       <c r="E160" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161">
-        <v>11767</v>
+        <v>7005</v>
       </c>
       <c r="B161" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161">
-        <v>184</v>
+        <v>368</v>
       </c>
       <c r="E161" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162">
-        <v>11772</v>
+        <v>7007</v>
       </c>
       <c r="B162" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162">
-        <v>144.5</v>
+        <v>375</v>
       </c>
       <c r="E162" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163">
-        <v>11812</v>
+        <v>7036</v>
       </c>
       <c r="B163" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163">
-        <v>113.5</v>
+        <v>229.5</v>
       </c>
       <c r="E163" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164">
-        <v>11813</v>
+        <v>7084</v>
       </c>
       <c r="B164" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164">
-        <v>96</v>
+        <v>1376</v>
       </c>
       <c r="E164" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165">
-        <v>11835</v>
+        <v>7084</v>
       </c>
       <c r="B165" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D165">
-        <v>124</v>
+        <v>229.25</v>
       </c>
       <c r="E165" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166">
-        <v>11859</v>
+        <v>7250</v>
       </c>
       <c r="B166" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C166">
         <v>1</v>
       </c>
       <c r="D166">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="E166" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167">
-        <v>11891</v>
+        <v>7250</v>
       </c>
       <c r="B167" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D167">
-        <v>816</v>
+        <v>54.5</v>
       </c>
       <c r="E167" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168">
-        <v>11891</v>
+        <v>7567</v>
       </c>
       <c r="B168" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C168">
         <v>3</v>
       </c>
       <c r="D168">
-        <v>68</v>
+        <v>424.5</v>
       </c>
       <c r="E168" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169">
-        <v>12346</v>
+        <v>7703</v>
       </c>
       <c r="B169" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D169">
-        <v>50</v>
+        <v>167.75</v>
       </c>
       <c r="E169" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170">
-        <v>12350</v>
+        <v>7705</v>
       </c>
       <c r="B170" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D170">
-        <v>49.75</v>
+        <v>167.25</v>
       </c>
       <c r="E170" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171">
-        <v>12373</v>
+        <v>7707</v>
       </c>
       <c r="B171" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C171">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171">
-        <v>58</v>
+        <v>167.25</v>
       </c>
       <c r="E171" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172">
-        <v>12512</v>
+        <v>8285</v>
       </c>
       <c r="B172" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
       <c r="D172">
-        <v>129</v>
+        <v>740.75</v>
       </c>
       <c r="E172" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173">
-        <v>12586</v>
+        <v>8285</v>
       </c>
       <c r="B173" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173">
-        <v>600</v>
+        <v>61.75</v>
       </c>
       <c r="E173" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174">
-        <v>12586</v>
+        <v>8648</v>
       </c>
       <c r="B174" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D174">
-        <v>50</v>
+        <v>160.5</v>
       </c>
       <c r="E174" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175">
-        <v>12588</v>
+        <v>8650</v>
       </c>
       <c r="B175" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175">
-        <v>606</v>
+        <v>164.75</v>
       </c>
       <c r="E175" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176">
-        <v>12588</v>
+        <v>8674</v>
       </c>
       <c r="B176" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C176">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D176">
-        <v>50.5</v>
+        <v>102.5</v>
       </c>
       <c r="E176" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177">
-        <v>12648</v>
+        <v>8675</v>
       </c>
       <c r="B177" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D177">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="E177" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178">
-        <v>12656</v>
+        <v>8676</v>
       </c>
       <c r="B178" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178">
-        <v>357</v>
+        <v>102</v>
       </c>
       <c r="E178" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179">
-        <v>12720</v>
+        <v>8853</v>
       </c>
       <c r="B179" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C179">
         <v>2</v>
       </c>
       <c r="D179">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E179" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180">
-        <v>13028</v>
+        <v>8915</v>
       </c>
       <c r="B180" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D180">
-        <v>203</v>
+        <v>184.75</v>
       </c>
       <c r="E180" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181">
-        <v>14018</v>
+        <v>8943</v>
       </c>
       <c r="B181" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C181">
         <v>1</v>
       </c>
       <c r="D181">
-        <v>1705</v>
+        <v>306</v>
       </c>
       <c r="E181" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182">
-        <v>14018</v>
+        <v>8943</v>
       </c>
       <c r="B182" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C182">
         <v>3</v>
       </c>
       <c r="D182">
-        <v>142</v>
+        <v>76.5</v>
       </c>
       <c r="E182" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183">
-        <v>14038</v>
+        <v>8945</v>
       </c>
       <c r="B183" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183">
-        <v>840</v>
+        <v>298.75</v>
       </c>
       <c r="E183" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184">
-        <v>14038</v>
+        <v>8945</v>
       </c>
       <c r="B184" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C184">
         <v>3</v>
       </c>
       <c r="D184">
-        <v>105</v>
+        <v>49.75</v>
       </c>
       <c r="E184" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185">
-        <v>19335</v>
+        <v>9507</v>
       </c>
       <c r="B185" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185">
-        <v>1097.75</v>
+        <v>870.5</v>
       </c>
       <c r="E185" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186">
-        <v>19335</v>
+        <v>9507</v>
       </c>
       <c r="B186" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C186">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D186">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="E186" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187">
-        <v>19981</v>
+        <v>9690</v>
       </c>
       <c r="B187" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187">
-        <v>455</v>
+        <v>405</v>
       </c>
       <c r="E187" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188">
-        <v>19984</v>
+        <v>9784</v>
       </c>
       <c r="B188" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D188">
-        <v>517.5</v>
+        <v>404.5</v>
       </c>
       <c r="E188" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189">
-        <v>19989</v>
+        <v>9785</v>
       </c>
       <c r="B189" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D189">
-        <v>455</v>
+        <v>405.5</v>
       </c>
       <c r="E189" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190">
-        <v>19997</v>
+        <v>9786</v>
       </c>
       <c r="B190" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D190">
-        <v>455</v>
+        <v>410.25</v>
       </c>
       <c r="E190" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191">
-        <v>21269</v>
+        <v>10408</v>
       </c>
       <c r="B191" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191">
-        <v>384</v>
+        <v>484</v>
       </c>
       <c r="E191" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192">
-        <v>21269</v>
+        <v>10408</v>
       </c>
       <c r="B192" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C192">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D192">
-        <v>96</v>
+        <v>40.25</v>
       </c>
       <c r="E192" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193">
-        <v>21807</v>
+        <v>10410</v>
       </c>
       <c r="B193" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="E193" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194">
-        <v>21946</v>
+        <v>10410</v>
       </c>
       <c r="B194" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C194">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D194">
-        <v>411.5</v>
+        <v>27.5</v>
       </c>
       <c r="E194" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195">
-        <v>22317</v>
+        <v>10574</v>
       </c>
       <c r="B195" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195">
-        <v>1116</v>
+        <v>1363.75</v>
       </c>
       <c r="E195" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196">
-        <v>22317</v>
+        <v>10574</v>
       </c>
       <c r="B196" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C196">
         <v>3</v>
       </c>
       <c r="D196">
-        <v>93</v>
+        <v>56.75</v>
       </c>
       <c r="E196" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197">
-        <v>23030</v>
+        <v>10993</v>
       </c>
       <c r="B197" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D197">
-        <v>1596</v>
+        <v>545</v>
       </c>
       <c r="E197" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198">
-        <v>23030</v>
+        <v>11164</v>
       </c>
       <c r="B198" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C198">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D198">
-        <v>133</v>
+        <v>73.25</v>
       </c>
       <c r="E198" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199">
-        <v>23031</v>
+        <v>11180</v>
       </c>
       <c r="B199" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199">
-        <v>1596</v>
+        <v>342.75</v>
       </c>
       <c r="E199" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200">
-        <v>23031</v>
+        <v>11234</v>
       </c>
       <c r="B200" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C200">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D200">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="E200" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201">
-        <v>23645</v>
+        <v>11490</v>
       </c>
       <c r="B201" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201">
-        <v>7311.25</v>
+        <v>277.5</v>
       </c>
       <c r="E201" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202">
-        <v>23645</v>
+        <v>11504</v>
       </c>
       <c r="B202" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C202">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D202">
-        <v>609.25</v>
+        <v>213.25</v>
       </c>
       <c r="E202" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203">
-        <v>24256</v>
+        <v>11737</v>
       </c>
       <c r="B203" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D203">
-        <v>212.5</v>
+        <v>497</v>
       </c>
       <c r="E203" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204">
-        <v>24257</v>
+        <v>11739</v>
       </c>
       <c r="B204" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204">
-        <v>212.5</v>
+        <v>497</v>
       </c>
       <c r="E204" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205">
-        <v>24566</v>
+        <v>12343</v>
       </c>
       <c r="B205" t="s">
+        <v>134</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="D205">
+        <v>49</v>
+      </c>
+      <c r="E205" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206">
+        <v>12344</v>
+      </c>
+      <c r="B206" t="s">
+        <v>135</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="D206">
+        <v>50.25</v>
+      </c>
+      <c r="E206" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207">
+        <v>12345</v>
+      </c>
+      <c r="B207" t="s">
+        <v>136</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="D207">
+        <v>49.5</v>
+      </c>
+      <c r="E207" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208">
+        <v>12346</v>
+      </c>
+      <c r="B208" t="s">
+        <v>137</v>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="D208">
+        <v>50</v>
+      </c>
+      <c r="E208" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209">
+        <v>12348</v>
+      </c>
+      <c r="B209" t="s">
+        <v>138</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209">
+        <v>49.5</v>
+      </c>
+      <c r="E209" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210">
+        <v>12350</v>
+      </c>
+      <c r="B210" t="s">
+        <v>139</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210">
+        <v>49.75</v>
+      </c>
+      <c r="E210" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211">
+        <v>12352</v>
+      </c>
+      <c r="B211" t="s">
+        <v>140</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+      <c r="D211">
+        <v>49.5</v>
+      </c>
+      <c r="E211" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212">
+        <v>12353</v>
+      </c>
+      <c r="B212" t="s">
+        <v>141</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212">
+        <v>49.25</v>
+      </c>
+      <c r="E212" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213">
+        <v>12373</v>
+      </c>
+      <c r="B213" t="s">
         <v>142</v>
       </c>
-      <c r="C205">
-        <v>1</v>
-      </c>
-      <c r="D205">
-        <v>90.25</v>
-      </c>
-      <c r="E205" t="s">
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="D213">
+        <v>55.25</v>
+      </c>
+      <c r="E213" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214">
+        <v>12720</v>
+      </c>
+      <c r="B214" t="s">
         <v>143</v>
+      </c>
+      <c r="C214">
+        <v>2</v>
+      </c>
+      <c r="D214">
+        <v>104</v>
+      </c>
+      <c r="E214" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215">
+        <v>12721</v>
+      </c>
+      <c r="B215" t="s">
+        <v>144</v>
+      </c>
+      <c r="C215">
+        <v>2</v>
+      </c>
+      <c r="D215">
+        <v>103</v>
+      </c>
+      <c r="E215" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216">
+        <v>13259</v>
+      </c>
+      <c r="B216" t="s">
+        <v>145</v>
+      </c>
+      <c r="C216">
+        <v>25</v>
+      </c>
+      <c r="D216">
+        <v>429</v>
+      </c>
+      <c r="E216" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217">
+        <v>13259</v>
+      </c>
+      <c r="B217" t="s">
+        <v>145</v>
+      </c>
+      <c r="C217">
+        <v>29</v>
+      </c>
+      <c r="D217">
+        <v>858</v>
+      </c>
+      <c r="E217" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218">
+        <v>13488</v>
+      </c>
+      <c r="B218" t="s">
+        <v>146</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218">
+        <v>240</v>
+      </c>
+      <c r="E218" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219">
+        <v>20255</v>
+      </c>
+      <c r="B219" t="s">
+        <v>147</v>
+      </c>
+      <c r="C219">
+        <v>2</v>
+      </c>
+      <c r="D219">
+        <v>335</v>
+      </c>
+      <c r="E219" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220">
+        <v>20927</v>
+      </c>
+      <c r="B220" t="s">
+        <v>148</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220">
+        <v>375</v>
+      </c>
+      <c r="E220" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221">
+        <v>21793</v>
+      </c>
+      <c r="B221" t="s">
+        <v>149</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="D221">
+        <v>124</v>
+      </c>
+      <c r="E221" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222">
+        <v>21798</v>
+      </c>
+      <c r="B222" t="s">
+        <v>150</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222">
+        <v>211.5</v>
+      </c>
+      <c r="E222" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223">
+        <v>22316</v>
+      </c>
+      <c r="B223" t="s">
+        <v>151</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223">
+        <v>1152</v>
+      </c>
+      <c r="E223" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224">
+        <v>22316</v>
+      </c>
+      <c r="B224" t="s">
+        <v>151</v>
+      </c>
+      <c r="C224">
+        <v>3</v>
+      </c>
+      <c r="D224">
+        <v>96</v>
+      </c>
+      <c r="E224" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225">
+        <v>22558</v>
+      </c>
+      <c r="B225" t="s">
+        <v>152</v>
+      </c>
+      <c r="C225">
+        <v>1</v>
+      </c>
+      <c r="D225">
+        <v>1500</v>
+      </c>
+      <c r="E225" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226">
+        <v>22558</v>
+      </c>
+      <c r="B226" t="s">
+        <v>152</v>
+      </c>
+      <c r="C226">
+        <v>3</v>
+      </c>
+      <c r="D226">
+        <v>62.5</v>
+      </c>
+      <c r="E226" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227">
+        <v>23234</v>
+      </c>
+      <c r="B227" t="s">
+        <v>153</v>
+      </c>
+      <c r="C227">
+        <v>25</v>
+      </c>
+      <c r="D227">
+        <v>311.5</v>
+      </c>
+      <c r="E227" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228">
+        <v>23234</v>
+      </c>
+      <c r="B228" t="s">
+        <v>153</v>
+      </c>
+      <c r="C228">
+        <v>29</v>
+      </c>
+      <c r="D228">
+        <v>934.75</v>
+      </c>
+      <c r="E228" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229">
+        <v>23380</v>
+      </c>
+      <c r="B229" t="s">
+        <v>154</v>
+      </c>
+      <c r="C229">
+        <v>25</v>
+      </c>
+      <c r="D229">
+        <v>319.25</v>
+      </c>
+      <c r="E229" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230">
+        <v>23380</v>
+      </c>
+      <c r="B230" t="s">
+        <v>154</v>
+      </c>
+      <c r="C230">
+        <v>29</v>
+      </c>
+      <c r="D230">
+        <v>957.5</v>
+      </c>
+      <c r="E230" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231">
+        <v>24127</v>
+      </c>
+      <c r="B231" t="s">
+        <v>155</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231">
+        <v>1207.5</v>
+      </c>
+      <c r="E231" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232">
+        <v>24127</v>
+      </c>
+      <c r="B232" t="s">
+        <v>155</v>
+      </c>
+      <c r="C232">
+        <v>3</v>
+      </c>
+      <c r="D232">
+        <v>120.75</v>
+      </c>
+      <c r="E232" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233">
+        <v>24256</v>
+      </c>
+      <c r="B233" t="s">
+        <v>156</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233">
+        <v>217</v>
+      </c>
+      <c r="E233" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234">
+        <v>24258</v>
+      </c>
+      <c r="B234" t="s">
+        <v>157</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234">
+        <v>212.5</v>
+      </c>
+      <c r="E234" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235">
+        <v>25278</v>
+      </c>
+      <c r="B235" t="s">
+        <v>158</v>
+      </c>
+      <c r="C235">
+        <v>2</v>
+      </c>
+      <c r="D235">
+        <v>103.5</v>
+      </c>
+      <c r="E235" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/1_new_1124.xlsx
+++ b/Uploads/1_new_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="35">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,85 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>فاين بيبي كبير مقاس4 عبوة اقتصادية- 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبي اصفر وسط مقاس3- 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبى اصفر ماكسي مقاس5- 84 حفاضة</t>
+    <t>ايليت  شوكولاتة بحشو كريمة البندق والكريسبي  - 1 كيلو</t>
+  </si>
+  <si>
+    <t>تونة دولفين قطع 140 جم + 10 جم - 150 جم</t>
+  </si>
+  <si>
+    <t>ايليت شوكولاتة بيضاء بحشو كريمة الشوكولاتة والكريسبي علبة حجم كبير توست - 1 كيلو</t>
+  </si>
+  <si>
+    <t>تونة دولفين قطعة واحدة بارد - 200 جم</t>
+  </si>
+  <si>
+    <t>حلاوة الرشيدى الميزان - 545 جم</t>
+  </si>
+  <si>
+    <t>بقسماط ناعم ريتش بيك - 10 كيلو</t>
+  </si>
+  <si>
+    <t>مولبد ماكسى مضغوطة حماية ضد البكتيريا طويل جدا فردى - 7 فوطة</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة حار - 140 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين قطع بارد - 185 جم</t>
+  </si>
+  <si>
+    <t>عسل البوادى اسود - 355 جم</t>
+  </si>
+  <si>
+    <t>عسل البوادى اسود - 190 جم</t>
+  </si>
+  <si>
+    <t>طحينة الرشيدى الميزان - 130 جم</t>
+  </si>
+  <si>
+    <t>سردين دولفين بارد - 125 جم</t>
+  </si>
+  <si>
+    <t>ايليت شوكولاتة بحشو كريمة الشيكولاتة البيضاء تويست مربعه - 1 كيلو</t>
+  </si>
+  <si>
+    <t>مولبد ماكسى مضغوطة طويل جدا 20 + 4 فوطة ميجا توفير - 24 فوطة</t>
+  </si>
+  <si>
+    <t>صلصة هارفست صفيح - 375 جم</t>
+  </si>
+  <si>
+    <t>ايليت شوكولاتة  بحشو كريمة الشيكولاتة البيضاء مدوره مينى سنجل - 1 كيلو</t>
+  </si>
+  <si>
+    <t>اولويز ماكسى سميكة فردى ملمس قطنى طويل - 8 فوطة</t>
+  </si>
+  <si>
+    <t>اولويز ماكسى سميكة طويل جدا نعومة قطنية - 7 فوطة</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة حار 170 جم + 30 جم - 200 جم</t>
+  </si>
+  <si>
+    <t>حلواني حلاوة طحينية سادة - 280 جم</t>
+  </si>
+  <si>
+    <t>البوادي حلاوه سبريد شيكولاته بالبندق- 300 جم</t>
+  </si>
+  <si>
+    <t>ايليت شوكولاتة بحشو كريمة البندق والكريسبي علبة حجم كبير تويست - 1 كيلو</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة بارد - 140 جم</t>
+  </si>
+  <si>
+    <t>%طحينة الرشيدى الميزان خصم 10 - 255 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين جولد فصوص حار - 170 جم</t>
+  </si>
+  <si>
+    <t>بقسماط ناعم ريتش بيك - 25 كيلو</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,104 +504,546 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>488</v>
+        <v>25586</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>351</v>
+        <v>195.75</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>488</v>
+        <v>3429</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>117</v>
+        <v>1088</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>891</v>
+        <v>25591</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>356</v>
+        <v>1175</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>891</v>
+        <v>947</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>119</v>
+        <v>2827.25</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>1682</v>
+        <v>1053</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>729</v>
       </c>
       <c r="D6">
-        <v>349</v>
+        <v>255.25</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>1682</v>
+        <v>26065</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>137</v>
+      </c>
+      <c r="D7">
+        <v>455.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>9122</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>418.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>1414</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>581.75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>944</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>668.75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>279</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>25586</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1175</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>2103</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>178</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>964</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>263</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>1409</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>1369.75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>25587</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>195.75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>9113</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>828.75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>390.5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>25588</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>195.75</v>
+      </c>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>2216</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20">
+        <v>15</v>
+      </c>
+      <c r="D20">
+        <v>95.25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>2217</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>96.25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>2859</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+      <c r="D22">
+        <v>824.75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>948</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>379.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>25591</v>
+      </c>
+      <c r="B24" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>174</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>195.75</v>
+      </c>
+      <c r="E24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>5343</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>168.75</v>
+      </c>
+      <c r="E25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25589</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>195.75</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>1413</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27">
+        <v>16</v>
+      </c>
+      <c r="D27">
+        <v>576.75</v>
+      </c>
+      <c r="E27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>25587</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1175</v>
+      </c>
+      <c r="E28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>965</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1200</v>
+      </c>
+      <c r="E29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>25588</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1175</v>
+      </c>
+      <c r="E30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>25589</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1175</v>
+      </c>
+      <c r="E31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>9877</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>2962.75</v>
+      </c>
+      <c r="E32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>26064</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33">
+        <v>137</v>
+      </c>
+      <c r="D33">
+        <v>1139</v>
+      </c>
+      <c r="E33" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/1_new_1124.xlsx
+++ b/Uploads/1_new_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,85 +37,49 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>ايليت  شوكولاتة بحشو كريمة البندق والكريسبي  - 1 كيلو</t>
+    <t>حفاضات بى بم كومفورت مقاس 4 - 35 حفاضة</t>
+  </si>
+  <si>
+    <t>اولويز ماكسى سميكة فردى ملمس قطنى طويل - 8 فوطة</t>
+  </si>
+  <si>
+    <t>حفاضات بى بم مقاس 5 - 35 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات بى بم كومفورت مقاس 1 - 35 حفاضة</t>
+  </si>
+  <si>
+    <t>حلواني حلاوة طحينية سادة - 575 جم</t>
+  </si>
+  <si>
+    <t>حلاوة الرشيدى الميزان - 545 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين قطع بارد - 185 جم</t>
+  </si>
+  <si>
+    <t>%طحينة الرشيدى الميزان خصم 10 - 255 جم</t>
+  </si>
+  <si>
+    <t>اولويز ماكسى سميكة طويل جدا نعومة قطنية - 7 فوطة</t>
   </si>
   <si>
     <t>تونة دولفين قطع 140 جم + 10 جم - 150 جم</t>
   </si>
   <si>
-    <t>ايليت شوكولاتة بيضاء بحشو كريمة الشوكولاتة والكريسبي علبة حجم كبير توست - 1 كيلو</t>
-  </si>
-  <si>
-    <t>تونة دولفين قطعة واحدة بارد - 200 جم</t>
-  </si>
-  <si>
-    <t>حلاوة الرشيدى الميزان - 545 جم</t>
-  </si>
-  <si>
-    <t>بقسماط ناعم ريتش بيك - 10 كيلو</t>
-  </si>
-  <si>
-    <t>مولبد ماكسى مضغوطة حماية ضد البكتيريا طويل جدا فردى - 7 فوطة</t>
-  </si>
-  <si>
-    <t>تونة دولفين مفتتة حار - 140 جم</t>
-  </si>
-  <si>
-    <t>تونة دولفين قطع بارد - 185 جم</t>
+    <t>ماكينة حلاقة جيليت فينوس ديزي 2 حريمى - 5 ماكينة</t>
+  </si>
+  <si>
+    <t>صلصة هارفست صفيح - 375 جم</t>
+  </si>
+  <si>
+    <t>حلواني حلاوة طحينية سادة - 280 جم</t>
   </si>
   <si>
     <t>عسل البوادى اسود - 355 جم</t>
   </si>
   <si>
-    <t>عسل البوادى اسود - 190 جم</t>
-  </si>
-  <si>
-    <t>طحينة الرشيدى الميزان - 130 جم</t>
-  </si>
-  <si>
-    <t>سردين دولفين بارد - 125 جم</t>
-  </si>
-  <si>
-    <t>ايليت شوكولاتة بحشو كريمة الشيكولاتة البيضاء تويست مربعه - 1 كيلو</t>
-  </si>
-  <si>
-    <t>مولبد ماكسى مضغوطة طويل جدا 20 + 4 فوطة ميجا توفير - 24 فوطة</t>
-  </si>
-  <si>
-    <t>صلصة هارفست صفيح - 375 جم</t>
-  </si>
-  <si>
-    <t>ايليت شوكولاتة  بحشو كريمة الشيكولاتة البيضاء مدوره مينى سنجل - 1 كيلو</t>
-  </si>
-  <si>
-    <t>اولويز ماكسى سميكة فردى ملمس قطنى طويل - 8 فوطة</t>
-  </si>
-  <si>
-    <t>اولويز ماكسى سميكة طويل جدا نعومة قطنية - 7 فوطة</t>
-  </si>
-  <si>
-    <t>تونة دولفين مفتتة حار 170 جم + 30 جم - 200 جم</t>
-  </si>
-  <si>
-    <t>حلواني حلاوة طحينية سادة - 280 جم</t>
-  </si>
-  <si>
     <t>البوادي حلاوه سبريد شيكولاته بالبندق- 300 جم</t>
-  </si>
-  <si>
-    <t>ايليت شوكولاتة بحشو كريمة البندق والكريسبي علبة حجم كبير تويست - 1 كيلو</t>
-  </si>
-  <si>
-    <t>تونة دولفين مفتتة بارد - 140 جم</t>
-  </si>
-  <si>
-    <t>%طحينة الرشيدى الميزان خصم 10 - 255 جم</t>
-  </si>
-  <si>
-    <t>تونة دولفين جولد فصوص حار - 170 جم</t>
-  </si>
-  <si>
-    <t>بقسماط ناعم ريتش بيك - 25 كيلو</t>
   </si>
   <si>
     <t>YES</t>
@@ -476,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -504,546 +468,308 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>25586</v>
+        <v>25994</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>195.75</v>
+        <v>866.75</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>3429</v>
+        <v>2216</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1088</v>
+        <v>381.5</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>25591</v>
+        <v>25995</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D4">
-        <v>1175</v>
+        <v>190.75</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>947</v>
+        <v>25991</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D5">
-        <v>2827.25</v>
+        <v>147.25</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>1053</v>
+        <v>3915</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6">
-        <v>729</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>255.25</v>
+        <v>466</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>26065</v>
+        <v>1053</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>137</v>
+        <v>729</v>
       </c>
       <c r="D7">
-        <v>455.5</v>
+        <v>255.25</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>9122</v>
+        <v>944</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D8">
-        <v>418.5</v>
+        <v>668.75</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>1414</v>
+        <v>25991</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D9">
-        <v>581.75</v>
+        <v>736.75</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>944</v>
+        <v>965</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>668.75</v>
+        <v>1200</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>71</v>
+        <v>2217</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
       <c r="D11">
-        <v>279</v>
+        <v>192.25</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>25586</v>
+        <v>3429</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D12">
-        <v>1175</v>
+        <v>544</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>2103</v>
+        <v>3598</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>178</v>
+        <v>1576.5</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>964</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14">
-        <v>263</v>
+        <v>390.5</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>1409</v>
+        <v>948</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
       <c r="C15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15">
-        <v>1369.75</v>
+        <v>189.75</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>25587</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>195.75</v>
+        <v>558</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>9113</v>
+        <v>5343</v>
       </c>
       <c r="B17" t="s">
         <v>21</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D17">
-        <v>828.75</v>
+        <v>168.75</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>66</v>
+        <v>25994</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="D18">
-        <v>390.5</v>
+        <v>173.25</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>25588</v>
+        <v>25995</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D19">
-        <v>195.75</v>
+        <v>953.5</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>2216</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20">
-        <v>15</v>
-      </c>
-      <c r="D20">
-        <v>95.25</v>
-      </c>
-      <c r="E20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>2217</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21">
-        <v>15</v>
-      </c>
-      <c r="D21">
-        <v>96.25</v>
-      </c>
-      <c r="E21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>2859</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22">
-        <v>16</v>
-      </c>
-      <c r="D22">
-        <v>824.75</v>
-      </c>
-      <c r="E22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>948</v>
-      </c>
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23">
-        <v>16</v>
-      </c>
-      <c r="D23">
-        <v>379.5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>25591</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>195.75</v>
-      </c>
-      <c r="E24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>5343</v>
-      </c>
-      <c r="B25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25">
-        <v>15</v>
-      </c>
-      <c r="D25">
-        <v>168.75</v>
-      </c>
-      <c r="E25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>25589</v>
-      </c>
-      <c r="B26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>195.75</v>
-      </c>
-      <c r="E26" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>1413</v>
-      </c>
-      <c r="B27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27">
-        <v>16</v>
-      </c>
-      <c r="D27">
-        <v>576.75</v>
-      </c>
-      <c r="E27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>25587</v>
-      </c>
-      <c r="B28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>1175</v>
-      </c>
-      <c r="E28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>965</v>
-      </c>
-      <c r="B29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>1200</v>
-      </c>
-      <c r="E29" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>25588</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1175</v>
-      </c>
-      <c r="E30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>25589</v>
-      </c>
-      <c r="B31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>1175</v>
-      </c>
-      <c r="E31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>9877</v>
-      </c>
-      <c r="B32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>2962.75</v>
-      </c>
-      <c r="E32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>26064</v>
-      </c>
-      <c r="B33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33">
-        <v>137</v>
-      </c>
-      <c r="D33">
-        <v>1139</v>
-      </c>
-      <c r="E33" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/1_new_1124.xlsx
+++ b/Uploads/1_new_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,49 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حفاضات بى بم كومفورت مقاس 4 - 35 حفاضة</t>
-  </si>
-  <si>
-    <t>اولويز ماكسى سميكة فردى ملمس قطنى طويل - 8 فوطة</t>
-  </si>
-  <si>
-    <t>حفاضات بى بم مقاس 5 - 35 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات بى بم كومفورت مقاس 1 - 35 حفاضة</t>
-  </si>
-  <si>
-    <t>حلواني حلاوة طحينية سادة - 575 جم</t>
-  </si>
-  <si>
-    <t>حلاوة الرشيدى الميزان - 545 جم</t>
-  </si>
-  <si>
-    <t>تونة دولفين قطع بارد - 185 جم</t>
-  </si>
-  <si>
-    <t>%طحينة الرشيدى الميزان خصم 10 - 255 جم</t>
-  </si>
-  <si>
-    <t>اولويز ماكسى سميكة طويل جدا نعومة قطنية - 7 فوطة</t>
-  </si>
-  <si>
-    <t>تونة دولفين قطع 140 جم + 10 جم - 150 جم</t>
-  </si>
-  <si>
-    <t>ماكينة حلاقة جيليت فينوس ديزي 2 حريمى - 5 ماكينة</t>
-  </si>
-  <si>
-    <t>صلصة هارفست صفيح - 375 جم</t>
-  </si>
-  <si>
-    <t>حلواني حلاوة طحينية سادة - 280 جم</t>
-  </si>
-  <si>
-    <t>عسل البوادى اسود - 355 جم</t>
-  </si>
-  <si>
-    <t>البوادي حلاوه سبريد شيكولاته بالبندق- 300 جم</t>
+    <t>بيبسى - 2.43 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -440,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -468,308 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>25994</v>
+        <v>589</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>866.75</v>
+        <v>223</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>2216</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>381.5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>25995</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>80</v>
-      </c>
-      <c r="D4">
-        <v>190.75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>25991</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>80</v>
-      </c>
-      <c r="D5">
-        <v>147.25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>3915</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>466</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>1053</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>729</v>
-      </c>
-      <c r="D7">
-        <v>255.25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>944</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>668.75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>25991</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>29</v>
-      </c>
-      <c r="D9">
-        <v>736.75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>965</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1200</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>2217</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>16</v>
-      </c>
-      <c r="D11">
-        <v>192.25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>3429</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>15</v>
-      </c>
-      <c r="D12">
-        <v>544</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>3598</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1576.5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>66</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14">
-        <v>16</v>
-      </c>
-      <c r="D14">
-        <v>390.5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>948</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15">
-        <v>15</v>
-      </c>
-      <c r="D15">
-        <v>189.75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>71</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>558</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>5343</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17">
-        <v>15</v>
-      </c>
-      <c r="D17">
-        <v>168.75</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>25994</v>
-      </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>80</v>
-      </c>
-      <c r="D18">
-        <v>173.25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>25995</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19">
-        <v>29</v>
-      </c>
-      <c r="D19">
-        <v>953.5</v>
-      </c>
-      <c r="E19" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
